--- a/Structure_Data/text.9.14/20260915_01/structure_factor_20260915_01.xlsx
+++ b/Structure_Data/text.9.14/20260915_01/structure_factor_20260915_01.xlsx
@@ -40,7 +40,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:D311"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -248,6 +248,3083 @@
         <v>35.7020608042988</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度 beta / Constrictivity (x)</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈半径 r_min (um)</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">孔体半径 r_max (um)</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度状态 / Constrictivity Status</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">侵入入口 / Intrusion Inlet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球心邻域 / Center Connectivity</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">算法版本 / Method</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">edt_critical_radii_closed_dilation_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半径采样 / Radius Sampling</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All positive EDT values</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius (um)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPSD (total volume fraction)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIP (total volume fraction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <v>0.226242065429688</v>
+      </c>
+      <c r="C30">
+        <v>0.223258972167969</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.5</v>
+      </c>
+      <c r="B31">
+        <v>0.226242065429688</v>
+      </c>
+      <c r="C31">
+        <v>0.223258972167969</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B32">
+        <v>0.0224800109863281</v>
+      </c>
+      <c r="C32">
+        <v>0.000110626220703125</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B33">
+        <v>0.000606536865234375</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34">
+        <v>0.000156402587890625</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>1.5</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">弦长分布 / Chord Length</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_voxel_runs_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>35527</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>0.834689109691221</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>0.535943915828488</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Axis</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Window-spanning lines</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full pore line policy</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one_period_censored</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.05</v>
+      </c>
+      <c r="B51">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.1</v>
+      </c>
+      <c r="B52">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.15</v>
+      </c>
+      <c r="B53">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.2</v>
+      </c>
+      <c r="B54">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.25</v>
+      </c>
+      <c r="B55">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.3</v>
+      </c>
+      <c r="B56">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.35</v>
+      </c>
+      <c r="B57">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.4</v>
+      </c>
+      <c r="B58">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.45</v>
+      </c>
+      <c r="B59">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.5</v>
+      </c>
+      <c r="B60">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.55</v>
+      </c>
+      <c r="B61">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.65</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.7</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.75</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.8</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.85</v>
+      </c>
+      <c r="B67">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.9</v>
+      </c>
+      <c r="B68">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.95</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.5</v>
+      </c>
+      <c r="B71">
+        <v>21265</v>
+      </c>
+      <c r="C71">
+        <v>0.598558842570439</v>
+      </c>
+      <c r="D71">
+        <v>0.598558842570439</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>1</v>
+      </c>
+      <c r="B72">
+        <v>8709</v>
+      </c>
+      <c r="C72">
+        <v>0.245137501055535</v>
+      </c>
+      <c r="D72">
+        <v>0.843696343625975</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>1.5</v>
+      </c>
+      <c r="B73">
+        <v>3294</v>
+      </c>
+      <c r="C73">
+        <v>0.0927182143158724</v>
+      </c>
+      <c r="D73">
+        <v>0.936414557941847</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>2</v>
+      </c>
+      <c r="B74">
+        <v>1295</v>
+      </c>
+      <c r="C74">
+        <v>0.036451149829707</v>
+      </c>
+      <c r="D74">
+        <v>0.972865707771554</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>2.5</v>
+      </c>
+      <c r="B75">
+        <v>537</v>
+      </c>
+      <c r="C75">
+        <v>0.0151152644467588</v>
+      </c>
+      <c r="D75">
+        <v>0.987980972218313</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>3</v>
+      </c>
+      <c r="B76">
+        <v>238</v>
+      </c>
+      <c r="C76">
+        <v>0.00669913023897318</v>
+      </c>
+      <c r="D76">
+        <v>0.994680102457286</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>3.5</v>
+      </c>
+      <c r="B77">
+        <v>119</v>
+      </c>
+      <c r="C77">
+        <v>0.00334956511948659</v>
+      </c>
+      <c r="D77">
+        <v>0.998029667576773</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>4</v>
+      </c>
+      <c r="B78">
+        <v>38</v>
+      </c>
+      <c r="C78">
+        <v>0.00106960902975202</v>
+      </c>
+      <c r="D78">
+        <v>0.999099276606525</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>4.5</v>
+      </c>
+      <c r="B79">
+        <v>19</v>
+      </c>
+      <c r="C79">
+        <v>0.00053480451487601</v>
+      </c>
+      <c r="D79">
+        <v>0.999634081121401</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>5</v>
+      </c>
+      <c r="B80">
+        <v>6</v>
+      </c>
+      <c r="C80">
+        <v>0.000168885636276635</v>
+      </c>
+      <c r="D80">
+        <v>0.999802966757677</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>5.5</v>
+      </c>
+      <c r="B81">
+        <v>3</v>
+      </c>
+      <c r="C81">
+        <v>8.44428181383173e-05</v>
+      </c>
+      <c r="D81">
+        <v>0.999887409575816</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>6</v>
+      </c>
+      <c r="B82">
+        <v>3</v>
+      </c>
+      <c r="C82">
+        <v>8.44428181383173e-05</v>
+      </c>
+      <c r="D82">
+        <v>0.999971852393954</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>6.5</v>
+      </c>
+      <c r="B83">
+        <v>1</v>
+      </c>
+      <c r="C83">
+        <v>2.81476060461058e-05</v>
+      </c>
+      <c r="D83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84"/>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球接触分布 / Spherical Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_solid_to_pore_edt_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>202836</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B92">
+        <v>0.64876303868314</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B93">
+        <v>0.248825357900361</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance direction</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solid_to_pore</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance convention</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voxel_center_to_voxel_center</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.05</v>
+      </c>
+      <c r="B98">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.1</v>
+      </c>
+      <c r="B99">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.15</v>
+      </c>
+      <c r="B100">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.2</v>
+      </c>
+      <c r="B101">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>0.25</v>
+      </c>
+      <c r="B102">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>0.3</v>
+      </c>
+      <c r="B103">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>0.35</v>
+      </c>
+      <c r="B104">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>0.4</v>
+      </c>
+      <c r="B105">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>0.45</v>
+      </c>
+      <c r="B106">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>0.5</v>
+      </c>
+      <c r="B107">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>0.55</v>
+      </c>
+      <c r="B108">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>0.6</v>
+      </c>
+      <c r="B109">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>0.65</v>
+      </c>
+      <c r="B110">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>0.7</v>
+      </c>
+      <c r="B111">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>0.75</v>
+      </c>
+      <c r="B112">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>0.8</v>
+      </c>
+      <c r="B113">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>0.85</v>
+      </c>
+      <c r="B114">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>0.9</v>
+      </c>
+      <c r="B115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>0.95</v>
+      </c>
+      <c r="B116">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>0.5</v>
+      </c>
+      <c r="B118">
+        <v>121823</v>
+      </c>
+      <c r="C118">
+        <v>0.600598513084462</v>
+      </c>
+      <c r="D118">
+        <v>0.600598513084462</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B119">
+        <v>50118</v>
+      </c>
+      <c r="C119">
+        <v>0.247086316038573</v>
+      </c>
+      <c r="D119">
+        <v>0.847684829123035</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B120">
+        <v>8684</v>
+      </c>
+      <c r="C120">
+        <v>0.0428129128951468</v>
+      </c>
+      <c r="D120">
+        <v>0.890497742018182</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>1</v>
+      </c>
+      <c r="B121">
+        <v>3920</v>
+      </c>
+      <c r="C121">
+        <v>0.0193259579167406</v>
+      </c>
+      <c r="D121">
+        <v>0.909823699934923</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B122">
+        <v>8201</v>
+      </c>
+      <c r="C122">
+        <v>0.0404316787946913</v>
+      </c>
+      <c r="D122">
+        <v>0.950255378729614</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B123">
+        <v>3732</v>
+      </c>
+      <c r="C123">
+        <v>0.0183991007513459</v>
+      </c>
+      <c r="D123">
+        <v>0.96865447948096</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B124">
+        <v>1398</v>
+      </c>
+      <c r="C124">
+        <v>0.00689226764479678</v>
+      </c>
+      <c r="D124">
+        <v>0.975546747125757</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>1.5</v>
+      </c>
+      <c r="B125">
+        <v>2215</v>
+      </c>
+      <c r="C125">
+        <v>0.0109201522412195</v>
+      </c>
+      <c r="D125">
+        <v>0.986466899366976</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B126">
+        <v>1019</v>
+      </c>
+      <c r="C126">
+        <v>0.0050237630400915</v>
+      </c>
+      <c r="D126">
+        <v>0.991490662407068</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B127">
+        <v>562</v>
+      </c>
+      <c r="C127">
+        <v>0.00277071131357353</v>
+      </c>
+      <c r="D127">
+        <v>0.994261373720641</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B128">
+        <v>141</v>
+      </c>
+      <c r="C128">
+        <v>0.000695142874046027</v>
+      </c>
+      <c r="D128">
+        <v>0.994956516594687</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B129">
+        <v>350</v>
+      </c>
+      <c r="C129">
+        <v>0.00172553195685184</v>
+      </c>
+      <c r="D129">
+        <v>0.996682048551539</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B130">
+        <v>342</v>
+      </c>
+      <c r="C130">
+        <v>0.00168609122640951</v>
+      </c>
+      <c r="D130">
+        <v>0.998368139777949</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>2</v>
+      </c>
+      <c r="B131">
+        <v>42</v>
+      </c>
+      <c r="C131">
+        <v>0.000207063834822221</v>
+      </c>
+      <c r="D131">
+        <v>0.998575203612771</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B132">
+        <v>151</v>
+      </c>
+      <c r="C132">
+        <v>0.000744443787098937</v>
+      </c>
+      <c r="D132">
+        <v>0.99931964739987</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>2.12132034355964</v>
+      </c>
+      <c r="B133">
+        <v>51</v>
+      </c>
+      <c r="C133">
+        <v>0.00025143465656984</v>
+      </c>
+      <c r="D133">
+        <v>0.99957108205644</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>2.17944947177034</v>
+      </c>
+      <c r="B134">
+        <v>21</v>
+      </c>
+      <c r="C134">
+        <v>0.00010353191741111</v>
+      </c>
+      <c r="D134">
+        <v>0.999674613973851</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>2.23606797749979</v>
+      </c>
+      <c r="B135">
+        <v>16</v>
+      </c>
+      <c r="C135">
+        <v>7.88814608846556e-05</v>
+      </c>
+      <c r="D135">
+        <v>0.999753495434735</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>2.29128784747792</v>
+      </c>
+      <c r="B136">
+        <v>23</v>
+      </c>
+      <c r="C136">
+        <v>0.000113392100021692</v>
+      </c>
+      <c r="D136">
+        <v>0.999866887534757</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>2.34520787991171</v>
+      </c>
+      <c r="B137">
+        <v>8</v>
+      </c>
+      <c r="C137">
+        <v>3.94407304423278e-05</v>
+      </c>
+      <c r="D137">
+        <v>0.999906328265199</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>2.44948974278318</v>
+      </c>
+      <c r="B138">
+        <v>5</v>
+      </c>
+      <c r="C138">
+        <v>2.46504565264549e-05</v>
+      </c>
+      <c r="D138">
+        <v>0.999930978721726</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>2.5</v>
+      </c>
+      <c r="B139">
+        <v>8</v>
+      </c>
+      <c r="C139">
+        <v>3.94407304423278e-05</v>
+      </c>
+      <c r="D139">
+        <v>0.999970419452168</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>2.54950975679639</v>
+      </c>
+      <c r="B140">
+        <v>5</v>
+      </c>
+      <c r="C140">
+        <v>2.46504565264549e-05</v>
+      </c>
+      <c r="D140">
+        <v>0.999995069908695</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>2.69258240356725</v>
+      </c>
+      <c r="B141">
+        <v>1</v>
+      </c>
+      <c r="C141">
+        <v>4.93009130529097e-06</v>
+      </c>
+      <c r="D141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142"/>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">两点相关函数 / Two-Point Correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_fft_radial_shells_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porosity</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>0.226242065429688</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radial bins</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bin_0_origin_only; bin_k: (k-1)*h &lt; distance &lt;= k*h</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normalization</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">joint_probability; C(0)=porosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius upper edge (um)</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displacement count</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean distance (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>0</v>
+      </c>
+      <c r="B153">
+        <v>0.226242065429688</v>
+      </c>
+      <c r="C153">
+        <v>1</v>
+      </c>
+      <c r="D153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>0.5</v>
+      </c>
+      <c r="B154">
+        <v>0.0922050476074219</v>
+      </c>
+      <c r="C154">
+        <v>6</v>
+      </c>
+      <c r="D154">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>1</v>
+      </c>
+      <c r="B155">
+        <v>0.0684077923114483</v>
+      </c>
+      <c r="C155">
+        <v>26</v>
+      </c>
+      <c r="D155">
+        <v>0.82359556171208</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>1.5</v>
+      </c>
+      <c r="B156">
+        <v>0.0551302591959635</v>
+      </c>
+      <c r="C156">
+        <v>90</v>
+      </c>
+      <c r="D156">
+        <v>1.31330283768748</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>2</v>
+      </c>
+      <c r="B157">
+        <v>0.0584191848982626</v>
+      </c>
+      <c r="C157">
+        <v>134</v>
+      </c>
+      <c r="D157">
+        <v>1.76619125712671</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>2.5</v>
+      </c>
+      <c r="B158">
+        <v>0.0578444724859193</v>
+      </c>
+      <c r="C158">
+        <v>258</v>
+      </c>
+      <c r="D158">
+        <v>2.25329087515144</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>3</v>
+      </c>
+      <c r="B159">
+        <v>0.0569249036835461</v>
+      </c>
+      <c r="C159">
+        <v>410</v>
+      </c>
+      <c r="D159">
+        <v>2.77015092047628</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>3.5</v>
+      </c>
+      <c r="B160">
+        <v>0.0566954516206193</v>
+      </c>
+      <c r="C160">
+        <v>494</v>
+      </c>
+      <c r="D160">
+        <v>3.26511495914839</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>4</v>
+      </c>
+      <c r="B161">
+        <v>0.056303980730582</v>
+      </c>
+      <c r="C161">
+        <v>690</v>
+      </c>
+      <c r="D161">
+        <v>3.74137726298534</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>4.5</v>
+      </c>
+      <c r="B162">
+        <v>0.0559135881134477</v>
+      </c>
+      <c r="C162">
+        <v>962</v>
+      </c>
+      <c r="D162">
+        <v>4.25479734207796</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>5</v>
+      </c>
+      <c r="B163">
+        <v>0.055603916744934</v>
+      </c>
+      <c r="C163">
+        <v>1098</v>
+      </c>
+      <c r="D163">
+        <v>4.75998893674797</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>5.5</v>
+      </c>
+      <c r="B164">
+        <v>0.0553055569253978</v>
+      </c>
+      <c r="C164">
+        <v>1406</v>
+      </c>
+      <c r="D164">
+        <v>5.25297061080461</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>6</v>
+      </c>
+      <c r="B165">
+        <v>0.0550011996231756</v>
+      </c>
+      <c r="C165">
+        <v>1578</v>
+      </c>
+      <c r="D165">
+        <v>5.7433060626392</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>6.5</v>
+      </c>
+      <c r="B166">
+        <v>0.0546670503493461</v>
+      </c>
+      <c r="C166">
+        <v>2018</v>
+      </c>
+      <c r="D166">
+        <v>6.24308779578354</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>7</v>
+      </c>
+      <c r="B167">
+        <v>0.0543804771364702</v>
+      </c>
+      <c r="C167">
+        <v>2342</v>
+      </c>
+      <c r="D167">
+        <v>6.75452277955052</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>7.5</v>
+      </c>
+      <c r="B168">
+        <v>0.0541124104910397</v>
+      </c>
+      <c r="C168">
+        <v>2634</v>
+      </c>
+      <c r="D168">
+        <v>7.25880828593797</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>8</v>
+      </c>
+      <c r="B169">
+        <v>0.0538301435346896</v>
+      </c>
+      <c r="C169">
+        <v>2930</v>
+      </c>
+      <c r="D169">
+        <v>7.7481595567505</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>8.5</v>
+      </c>
+      <c r="B170">
+        <v>0.0535837405573123</v>
+      </c>
+      <c r="C170">
+        <v>3402</v>
+      </c>
+      <c r="D170">
+        <v>8.24275983872338</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>9</v>
+      </c>
+      <c r="B171">
+        <v>0.053317083124597</v>
+      </c>
+      <c r="C171">
+        <v>3926</v>
+      </c>
+      <c r="D171">
+        <v>8.74722614715433</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>9.5</v>
+      </c>
+      <c r="B172">
+        <v>0.0530365158345741</v>
+      </c>
+      <c r="C172">
+        <v>4266</v>
+      </c>
+      <c r="D172">
+        <v>9.24875254641385</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>10</v>
+      </c>
+      <c r="B173">
+        <v>0.0527847919101191</v>
+      </c>
+      <c r="C173">
+        <v>4730</v>
+      </c>
+      <c r="D173">
+        <v>9.74564847205822</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>10.5</v>
+      </c>
+      <c r="B174">
+        <v>0.0525494016450027</v>
+      </c>
+      <c r="C174">
+        <v>5510</v>
+      </c>
+      <c r="D174">
+        <v>10.2542063522575</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>11</v>
+      </c>
+      <c r="B175">
+        <v>0.0523511302938396</v>
+      </c>
+      <c r="C175">
+        <v>5562</v>
+      </c>
+      <c r="D175">
+        <v>10.7542478228895</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>11.5</v>
+      </c>
+      <c r="B176">
+        <v>0.0521512785865439</v>
+      </c>
+      <c r="C176">
+        <v>6410</v>
+      </c>
+      <c r="D176">
+        <v>11.244987895373</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>12</v>
+      </c>
+      <c r="B177">
+        <v>0.0519611767004426</v>
+      </c>
+      <c r="C177">
+        <v>6894</v>
+      </c>
+      <c r="D177">
+        <v>11.7450714339387</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>12.5</v>
+      </c>
+      <c r="B178">
+        <v>0.0517750779522436</v>
+      </c>
+      <c r="C178">
+        <v>7490</v>
+      </c>
+      <c r="D178">
+        <v>12.2441426243554</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>13</v>
+      </c>
+      <c r="B179">
+        <v>0.0515832621527515</v>
+      </c>
+      <c r="C179">
+        <v>8258</v>
+      </c>
+      <c r="D179">
+        <v>12.7444225452559</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>13.5</v>
+      </c>
+      <c r="B180">
+        <v>0.0514373762331355</v>
+      </c>
+      <c r="C180">
+        <v>8994</v>
+      </c>
+      <c r="D180">
+        <v>13.2528519154988</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>14</v>
+      </c>
+      <c r="B181">
+        <v>0.0512795667387837</v>
+      </c>
+      <c r="C181">
+        <v>9446</v>
+      </c>
+      <c r="D181">
+        <v>13.7542803671108</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>14.5</v>
+      </c>
+      <c r="B182">
+        <v>0.051136085661649</v>
+      </c>
+      <c r="C182">
+        <v>9978</v>
+      </c>
+      <c r="D182">
+        <v>14.2483018118451</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>15</v>
+      </c>
+      <c r="B183">
+        <v>0.0510067507359728</v>
+      </c>
+      <c r="C183">
+        <v>11138</v>
+      </c>
+      <c r="D183">
+        <v>14.7478143756516</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>15.5</v>
+      </c>
+      <c r="B184">
+        <v>0.0508892534909156</v>
+      </c>
+      <c r="C184">
+        <v>11406</v>
+      </c>
+      <c r="D184">
+        <v>15.2452282287867</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>16</v>
+      </c>
+      <c r="B185">
+        <v>0.0507799073479048</v>
+      </c>
+      <c r="C185">
+        <v>12575</v>
+      </c>
+      <c r="D185">
+        <v>15.7433814113418</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>16.5</v>
+      </c>
+      <c r="B186">
+        <v>0.050675447376104</v>
+      </c>
+      <c r="C186">
+        <v>12848</v>
+      </c>
+      <c r="D186">
+        <v>16.2480191911098</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>17</v>
+      </c>
+      <c r="B187">
+        <v>0.0505252502846283</v>
+      </c>
+      <c r="C187">
+        <v>12060</v>
+      </c>
+      <c r="D187">
+        <v>16.7498118527173</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>17.5</v>
+      </c>
+      <c r="B188">
+        <v>0.050410014417203</v>
+      </c>
+      <c r="C188">
+        <v>11804</v>
+      </c>
+      <c r="D188">
+        <v>17.2477889982035</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>18</v>
+      </c>
+      <c r="B189">
+        <v>0.0503077842917404</v>
+      </c>
+      <c r="C189">
+        <v>11016</v>
+      </c>
+      <c r="D189">
+        <v>17.7466461218484</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>18.5</v>
+      </c>
+      <c r="B190">
+        <v>0.050234945422021</v>
+      </c>
+      <c r="C190">
+        <v>10700</v>
+      </c>
+      <c r="D190">
+        <v>18.2476461964778</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>19</v>
+      </c>
+      <c r="B191">
+        <v>0.0501638719809744</v>
+      </c>
+      <c r="C191">
+        <v>9756</v>
+      </c>
+      <c r="D191">
+        <v>18.7461608461768</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>19.5</v>
+      </c>
+      <c r="B192">
+        <v>0.0501090766860419</v>
+      </c>
+      <c r="C192">
+        <v>9224</v>
+      </c>
+      <c r="D192">
+        <v>19.2443623593903</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>20</v>
+      </c>
+      <c r="B193">
+        <v>0.0500449598913075</v>
+      </c>
+      <c r="C193">
+        <v>8408</v>
+      </c>
+      <c r="D193">
+        <v>19.7427539394596</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>20.5</v>
+      </c>
+      <c r="B194">
+        <v>0.0500286499531245</v>
+      </c>
+      <c r="C194">
+        <v>7452</v>
+      </c>
+      <c r="D194">
+        <v>20.2349524648069</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>21</v>
+      </c>
+      <c r="B195">
+        <v>0.0499898834662004</v>
+      </c>
+      <c r="C195">
+        <v>7040</v>
+      </c>
+      <c r="D195">
+        <v>20.7366941177926</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>21.5</v>
+      </c>
+      <c r="B196">
+        <v>0.0499421739086662</v>
+      </c>
+      <c r="C196">
+        <v>5820</v>
+      </c>
+      <c r="D196">
+        <v>21.2419860619221</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <v>22</v>
+      </c>
+      <c r="B197">
+        <v>0.0499372904417945</v>
+      </c>
+      <c r="C197">
+        <v>4880</v>
+      </c>
+      <c r="D197">
+        <v>21.7372039907627</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <v>22.5</v>
+      </c>
+      <c r="B198">
+        <v>0.0499565271827264</v>
+      </c>
+      <c r="C198">
+        <v>3936</v>
+      </c>
+      <c r="D198">
+        <v>22.2302479362391</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <v>23</v>
+      </c>
+      <c r="B199">
+        <v>0.0499449014743196</v>
+      </c>
+      <c r="C199">
+        <v>2999</v>
+      </c>
+      <c r="D199">
+        <v>22.7334385317465</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <v>23.5</v>
+      </c>
+      <c r="B200">
+        <v>0.0499366550270571</v>
+      </c>
+      <c r="C200">
+        <v>2180</v>
+      </c>
+      <c r="D200">
+        <v>23.2369587045059</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201">
+        <v>24</v>
+      </c>
+      <c r="B201">
+        <v>0.0498944364948037</v>
+      </c>
+      <c r="C201">
+        <v>1620</v>
+      </c>
+      <c r="D201">
+        <v>23.7279225769148</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202">
+        <v>24.5</v>
+      </c>
+      <c r="B202">
+        <v>0.0498967265451191</v>
+      </c>
+      <c r="C202">
+        <v>1208</v>
+      </c>
+      <c r="D202">
+        <v>24.2151258882127</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203">
+        <v>25</v>
+      </c>
+      <c r="B203">
+        <v>0.0498887728227425</v>
+      </c>
+      <c r="C203">
+        <v>942</v>
+      </c>
+      <c r="D203">
+        <v>24.7383759194601</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204">
+        <v>25.5</v>
+      </c>
+      <c r="B204">
+        <v>0.0498279284124505</v>
+      </c>
+      <c r="C204">
+        <v>584</v>
+      </c>
+      <c r="D204">
+        <v>25.2823739766508</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205">
+        <v>26</v>
+      </c>
+      <c r="B205">
+        <v>0.0498277905961158</v>
+      </c>
+      <c r="C205">
+        <v>284</v>
+      </c>
+      <c r="D205">
+        <v>25.7666230311241</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206">
+        <v>26.5</v>
+      </c>
+      <c r="B206">
+        <v>0.0498578548431396</v>
+      </c>
+      <c r="C206">
+        <v>192</v>
+      </c>
+      <c r="D206">
+        <v>26.1687296580041</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207">
+        <v>27</v>
+      </c>
+      <c r="B207">
+        <v>0.0497879615196815</v>
+      </c>
+      <c r="C207">
+        <v>104</v>
+      </c>
+      <c r="D207">
+        <v>26.6774814912972</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208">
+        <v>27.5</v>
+      </c>
+      <c r="B208">
+        <v>0.0498600006103516</v>
+      </c>
+      <c r="C208">
+        <v>24</v>
+      </c>
+      <c r="D208">
+        <v>27.2129968013123</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209">
+        <v>28</v>
+      </c>
+      <c r="B209">
+        <v>0.0500335693359375</v>
+      </c>
+      <c r="C209">
+        <v>1</v>
+      </c>
+      <c r="D209">
+        <v>27.712812921102</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x displacement (um)</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211">
+        <v>0</v>
+      </c>
+      <c r="B211">
+        <v>0.226242065429688</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212">
+        <v>0.5</v>
+      </c>
+      <c r="B212">
+        <v>0.0907173156738281</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213">
+        <v>1</v>
+      </c>
+      <c r="B213">
+        <v>0.0607872009277344</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214">
+        <v>1.5</v>
+      </c>
+      <c r="B214">
+        <v>0.0566177368164062</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215">
+        <v>2</v>
+      </c>
+      <c r="B215">
+        <v>0.059600830078125</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <v>2.5</v>
+      </c>
+      <c r="B216">
+        <v>0.0568923950195312</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <v>3</v>
+      </c>
+      <c r="B217">
+        <v>0.0554962158203125</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <v>3.5</v>
+      </c>
+      <c r="B218">
+        <v>0.0561408996582031</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>4</v>
+      </c>
+      <c r="B219">
+        <v>0.0558815002441406</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>4.5</v>
+      </c>
+      <c r="B220">
+        <v>0.0551109313964844</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>5</v>
+      </c>
+      <c r="B221">
+        <v>0.054779052734375</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>5.5</v>
+      </c>
+      <c r="B222">
+        <v>0.0542945861816406</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>6</v>
+      </c>
+      <c r="B223">
+        <v>0.0535926818847656</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>6.5</v>
+      </c>
+      <c r="B224">
+        <v>0.0532417297363281</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>7</v>
+      </c>
+      <c r="B225">
+        <v>0.0528602600097656</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <v>7.5</v>
+      </c>
+      <c r="B226">
+        <v>0.0526351928710938</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <v>8</v>
+      </c>
+      <c r="B227">
+        <v>0.0520133972167969</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <v>8.5</v>
+      </c>
+      <c r="B228">
+        <v>0.0516471862792969</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229">
+        <v>9</v>
+      </c>
+      <c r="B229">
+        <v>0.0516891479492188</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230">
+        <v>9.5</v>
+      </c>
+      <c r="B230">
+        <v>0.05133056640625</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231">
+        <v>10</v>
+      </c>
+      <c r="B231">
+        <v>0.0514678955078125</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232">
+        <v>10.5</v>
+      </c>
+      <c r="B232">
+        <v>0.0513877868652344</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <v>11</v>
+      </c>
+      <c r="B233">
+        <v>0.0504379272460938</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234">
+        <v>11.5</v>
+      </c>
+      <c r="B234">
+        <v>0.0496940612792969</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235">
+        <v>12</v>
+      </c>
+      <c r="B235">
+        <v>0.0503768920898438</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236">
+        <v>12.5</v>
+      </c>
+      <c r="B236">
+        <v>0.0500717163085938</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>13</v>
+      </c>
+      <c r="B237">
+        <v>0.0499916076660156</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>13.5</v>
+      </c>
+      <c r="B238">
+        <v>0.0496749877929688</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>14</v>
+      </c>
+      <c r="B239">
+        <v>0.0499038696289062</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>14.5</v>
+      </c>
+      <c r="B240">
+        <v>0.0494041442871094</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>15</v>
+      </c>
+      <c r="B241">
+        <v>0.0495719909667969</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>15.5</v>
+      </c>
+      <c r="B242">
+        <v>0.0494422912597656</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>16</v>
+      </c>
+      <c r="B243">
+        <v>0.049530029296875</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y displacement (um)</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>0</v>
+      </c>
+      <c r="B245">
+        <v>0.226242065429688</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>0.5</v>
+      </c>
+      <c r="B246">
+        <v>0.0905532836914062</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>1</v>
+      </c>
+      <c r="B247">
+        <v>0.0594978332519531</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>1.5</v>
+      </c>
+      <c r="B248">
+        <v>0.0554161071777344</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>2</v>
+      </c>
+      <c r="B249">
+        <v>0.0580558776855469</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>2.5</v>
+      </c>
+      <c r="B250">
+        <v>0.0564804077148438</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>3</v>
+      </c>
+      <c r="B251">
+        <v>0.057220458984375</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>3.5</v>
+      </c>
+      <c r="B252">
+        <v>0.0565223693847656</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>4</v>
+      </c>
+      <c r="B253">
+        <v>0.0557670593261719</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>4.5</v>
+      </c>
+      <c r="B254">
+        <v>0.0556068420410156</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>5</v>
+      </c>
+      <c r="B255">
+        <v>0.0550651550292969</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>5.5</v>
+      </c>
+      <c r="B256">
+        <v>0.0547409057617188</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>6</v>
+      </c>
+      <c r="B257">
+        <v>0.0544586181640625</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>6.5</v>
+      </c>
+      <c r="B258">
+        <v>0.0541648864746094</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>7</v>
+      </c>
+      <c r="B259">
+        <v>0.0533714294433594</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <v>7.5</v>
+      </c>
+      <c r="B260">
+        <v>0.0534019470214844</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <v>8</v>
+      </c>
+      <c r="B261">
+        <v>0.0536537170410156</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>8.5</v>
+      </c>
+      <c r="B262">
+        <v>0.0527229309082031</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <v>9</v>
+      </c>
+      <c r="B263">
+        <v>0.0532417297363281</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <v>9.5</v>
+      </c>
+      <c r="B264">
+        <v>0.0527076721191406</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <v>10</v>
+      </c>
+      <c r="B265">
+        <v>0.0518531799316406</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>10.5</v>
+      </c>
+      <c r="B266">
+        <v>0.0522689819335938</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>11</v>
+      </c>
+      <c r="B267">
+        <v>0.0517845153808594</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>11.5</v>
+      </c>
+      <c r="B268">
+        <v>0.0514984130859375</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>12</v>
+      </c>
+      <c r="B269">
+        <v>0.0507125854492188</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>12.5</v>
+      </c>
+      <c r="B270">
+        <v>0.0510520935058594</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>13</v>
+      </c>
+      <c r="B271">
+        <v>0.0510292053222656</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272">
+        <v>13.5</v>
+      </c>
+      <c r="B272">
+        <v>0.0503921508789062</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <v>14</v>
+      </c>
+      <c r="B273">
+        <v>0.0504531860351562</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>14.5</v>
+      </c>
+      <c r="B274">
+        <v>0.0501747131347656</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>15</v>
+      </c>
+      <c r="B275">
+        <v>0.0500030517578125</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>15.5</v>
+      </c>
+      <c r="B276">
+        <v>0.0508041381835938</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>16</v>
+      </c>
+      <c r="B277">
+        <v>0.0507659912109375</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z displacement (um)</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>0</v>
+      </c>
+      <c r="B279">
+        <v>0.226242065429688</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <v>0.5</v>
+      </c>
+      <c r="B280">
+        <v>0.0953445434570312</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <v>1</v>
+      </c>
+      <c r="B281">
+        <v>0.0612411499023438</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <v>1.5</v>
+      </c>
+      <c r="B282">
+        <v>0.0546722412109375</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <v>2</v>
+      </c>
+      <c r="B283">
+        <v>0.0595588684082031</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <v>2.5</v>
+      </c>
+      <c r="B284">
+        <v>0.05810546875</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>3</v>
+      </c>
+      <c r="B285">
+        <v>0.0579452514648438</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <v>3.5</v>
+      </c>
+      <c r="B286">
+        <v>0.0579338073730469</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <v>4</v>
+      </c>
+      <c r="B287">
+        <v>0.0568199157714844</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <v>4.5</v>
+      </c>
+      <c r="B288">
+        <v>0.0562934875488281</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <v>5</v>
+      </c>
+      <c r="B289">
+        <v>0.0565147399902344</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290">
+        <v>5.5</v>
+      </c>
+      <c r="B290">
+        <v>0.0564918518066406</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291">
+        <v>6</v>
+      </c>
+      <c r="B291">
+        <v>0.0564422607421875</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292">
+        <v>6.5</v>
+      </c>
+      <c r="B292">
+        <v>0.0565452575683594</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293">
+        <v>7</v>
+      </c>
+      <c r="B293">
+        <v>0.05633544921875</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294">
+        <v>7.5</v>
+      </c>
+      <c r="B294">
+        <v>0.0556068420410156</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295">
+        <v>8</v>
+      </c>
+      <c r="B295">
+        <v>0.0556678771972656</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296">
+        <v>8.5</v>
+      </c>
+      <c r="B296">
+        <v>0.0555610656738281</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297">
+        <v>9</v>
+      </c>
+      <c r="B297">
+        <v>0.0551681518554688</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298">
+        <v>9.5</v>
+      </c>
+      <c r="B298">
+        <v>0.0548629760742188</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299">
+        <v>10</v>
+      </c>
+      <c r="B299">
+        <v>0.0550804138183594</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300">
+        <v>10.5</v>
+      </c>
+      <c r="B300">
+        <v>0.0552177429199219</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301">
+        <v>11</v>
+      </c>
+      <c r="B301">
+        <v>0.0547103881835938</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302">
+        <v>11.5</v>
+      </c>
+      <c r="B302">
+        <v>0.0559921264648438</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303">
+        <v>12</v>
+      </c>
+      <c r="B303">
+        <v>0.055267333984375</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304">
+        <v>12.5</v>
+      </c>
+      <c r="B304">
+        <v>0.0544090270996094</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305">
+        <v>13</v>
+      </c>
+      <c r="B305">
+        <v>0.0548324584960938</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306">
+        <v>13.5</v>
+      </c>
+      <c r="B306">
+        <v>0.0546913146972656</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307">
+        <v>14</v>
+      </c>
+      <c r="B307">
+        <v>0.0541915893554688</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308">
+        <v>14.5</v>
+      </c>
+      <c r="B308">
+        <v>0.0539016723632812</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309">
+        <v>15</v>
+      </c>
+      <c r="B309">
+        <v>0.0544548034667969</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310">
+        <v>15.5</v>
+      </c>
+      <c r="B310">
+        <v>0.055206298828125</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311">
+        <v>16</v>
+      </c>
+      <c r="B311">
+        <v>0.0556259155273437</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>